--- a/inst/extdata/gaz.xlsx
+++ b/inst/extdata/gaz.xlsx
@@ -5956,6 +5956,23 @@
         <v>9.41379839553539</v>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>11449.205</v>
+      </c>
+      <c r="B330" s="1" t="n">
+        <v>46121.59375</v>
+      </c>
+      <c r="C330" t="n">
+        <v>57.9220000000005</v>
+      </c>
+      <c r="D330" t="n">
+        <v>12.1791666666667</v>
+      </c>
+      <c r="E330" t="n">
+        <v>4.75582620595283</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/inst/extdata/gaz.xlsx
+++ b/inst/extdata/gaz.xlsx
@@ -5973,6 +5973,57 @@
         <v>4.75582620595283</v>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>11519.8278</v>
+      </c>
+      <c r="B331" s="1" t="n">
+        <v>46148.2694444444</v>
+      </c>
+      <c r="C331" t="n">
+        <v>70.6227999999992</v>
+      </c>
+      <c r="D331" t="n">
+        <v>26.6756944444444</v>
+      </c>
+      <c r="E331" t="n">
+        <v>2.64745872491081</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>11554.5378</v>
+      </c>
+      <c r="B332" s="1" t="n">
+        <v>46180.3631944444</v>
+      </c>
+      <c r="C332" t="n">
+        <v>34.7100000000009</v>
+      </c>
+      <c r="D332" t="n">
+        <v>32.09375</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1.0815189873418</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>11594.1</v>
+      </c>
+      <c r="B333" s="1" t="n">
+        <v>46250.7076388889</v>
+      </c>
+      <c r="C333" t="n">
+        <v>39.5622000000003</v>
+      </c>
+      <c r="D333" t="n">
+        <v>70.3444444444444</v>
+      </c>
+      <c r="E333" t="n">
+        <v>0.562406886747753</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
